--- a/file_upload_forms/046_user_data_upload_form--file_upload_forms.xlsx
+++ b/file_upload_forms/046_user_data_upload_form--file_upload_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1178,8 +1178,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'image',_'label':_'image'}</t>
+          <t>image</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'image', 'label': 'Image'}</t>
+          <t>Image</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'document',_'label':_'document'}</t>
+          <t>document</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'document', 'label': 'Document'}</t>
+          <t>Document</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'video',_'label':_'video'}</t>
+          <t>video</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'video', 'label': 'Video'}</t>
+          <t>Video</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'chatjimmy',_'label':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'chatjimmy', 'label': 'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'someone_else',_'label':_'someone_else'}</t>
+          <t>someone_else</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'someone_else', 'label': 'Someone Else'}</t>
+          <t>Someone Else</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'uploaded_by_user',_'label':_'uploaded_by_user'}</t>
+          <t>uploaded_by_user</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'uploaded_by_user', 'label': 'uploaded_by_user'}</t>
+          <t>uploaded by user</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'automated_system',_'label':_'automated_system'}</t>
+          <t>automated_system</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'automated_system', 'label': 'Automated System'}</t>
+          <t>Automated System</t>
         </is>
       </c>
     </row>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'uploaded_user',_'label':_'uploaded_user'}</t>
+          <t>uploaded_user</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'uploaded_user', 'label': 'uploaded_user'}</t>
+          <t>uploaded user</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1360,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'completed',_'label':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'completed', 'label': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1377,12 +1377,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'pending',_'label':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'pending', 'label': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1394,12 +1394,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'failed',_'label':_'failed'}</t>
+          <t>failed</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'failed', 'label': 'Failed'}</t>
+          <t>Failed</t>
         </is>
       </c>
     </row>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'group_a',_'label':_'group_a'}</t>
+          <t>group_a</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'group_a', 'label': 'Group A'}</t>
+          <t>Group A</t>
         </is>
       </c>
     </row>
@@ -1428,12 +1428,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'group_b',_'label':_'group_b'}</t>
+          <t>group_b</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'group_b', 'label': 'Group B'}</t>
+          <t>Group B</t>
         </is>
       </c>
     </row>
